--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91515</v>
+        <v>91517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87391</v>
+        <v>87393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91517</v>
+        <v>91519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87393</v>
+        <v>87395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91519</v>
+        <v>91520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87395</v>
+        <v>87396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87506</v>
+        <v>87512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87396</v>
+        <v>87402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87512</v>
+        <v>87516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87402</v>
+        <v>87406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87516</v>
+        <v>87518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87406</v>
+        <v>87408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91532</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87518</v>
+        <v>87531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87408</v>
+        <v>87421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87531</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87421</v>
+        <v>87423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91547</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87423</v>
+        <v>87426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87426</v>
+        <v>87436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87547</v>
+        <v>87550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91566</v>
+        <v>91571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87550</v>
+        <v>87555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87440</v>
+        <v>87445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18112-2025 artfynd.xlsx
+++ b/artfynd/A 18112-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866628</v>
       </c>
       <c r="B2" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866622</v>
       </c>
       <c r="B3" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866629</v>
       </c>
       <c r="B4" t="n">
-        <v>91571</v>
+        <v>91583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866624</v>
       </c>
       <c r="B5" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866627</v>
       </c>
       <c r="B6" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866631</v>
       </c>
       <c r="B7" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136866623</v>
       </c>
       <c r="B8" t="n">
-        <v>87555</v>
+        <v>87566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136866626</v>
       </c>
       <c r="B9" t="n">
-        <v>87445</v>
+        <v>87456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
